--- a/main/ig/ValueSet-fr-core-vs-patient-identifier-use.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-patient-identifier-use.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
